--- a/Results/public_data/gdsc_ploidy_analysis/runs/post_cleanup_check_gdsc/drug_count_collapsed/drug_count_collapsed_drugsVsPloidyCorr_Z_SCORE.xlsx
+++ b/Results/public_data/gdsc_ploidy_analysis/runs/post_cleanup_check_gdsc/drug_count_collapsed/drug_count_collapsed_drugsVsPloidyCorr_Z_SCORE.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">Serine/threonine kinase inhibitors</t>
+    <t xml:space="preserve">Kinase inhibitors</t>
   </si>
   <si>
     <t xml:space="preserve">Epigenetic inhibitors</t>
@@ -27,10 +27,7 @@
     <t xml:space="preserve">Other</t>
   </si>
   <si>
-    <t xml:space="preserve">Receptor tyrosine kinase inhibitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNA damage repair inhibitors</t>
+    <t xml:space="preserve">DNA damage and repair agents</t>
   </si>
   <si>
     <t xml:space="preserve">Metabolic/redox agents</t>
@@ -39,9 +36,6 @@
     <t xml:space="preserve">Proapoptotic agents</t>
   </si>
   <si>
-    <t xml:space="preserve">Non-receptor tyrosine kinase inhibitors</t>
-  </si>
-  <si>
     <t xml:space="preserve">WNT/HH pathway inhibitors</t>
   </si>
   <si>
@@ -49,9 +43,6 @@
   </si>
   <si>
     <t xml:space="preserve">Chaperone/protein-homeostasis inhibitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNA-damaging agents</t>
   </si>
   <si>
     <t xml:space="preserve">Antimitotic agents</t>
@@ -507,22 +498,13 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B2" t="n">
-        <v>0.916666666666667</v>
+        <v>0.993333333333333</v>
       </c>
       <c r="C2" t="n">
         <v>0.853333333333333</v>
@@ -531,528 +513,438 @@
         <v>0.11</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0366666666666667</v>
+        <v>0.896666666666667</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9</v>
+        <v>0.263333333333333</v>
       </c>
       <c r="H2" t="n">
-        <v>0.273333333333333</v>
+        <v>0.993333333333333</v>
       </c>
       <c r="I2" t="n">
-        <v>0.88</v>
+        <v>0.00666666666666667</v>
       </c>
       <c r="J2" t="n">
-        <v>0.983333333333333</v>
+        <v>0.746666666666667</v>
       </c>
       <c r="K2" t="n">
+        <v>0.00333333333333333</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.743333333333333</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.693333333333333</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.00333333333333333</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.00333333333333333</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.296666666666667</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.713333333333333</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.0333333333333333</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0366666666666667</v>
+        <v>0.793333333333333</v>
       </c>
       <c r="C3" t="n">
-        <v>0.91</v>
+        <v>0.923333333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>0.296666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.11</v>
       </c>
       <c r="F3" t="n">
-        <v>0.213333333333333</v>
+        <v>0.586666666666667</v>
       </c>
       <c r="G3" t="n">
-        <v>0.533333333333333</v>
+        <v>0.0566666666666667</v>
       </c>
       <c r="H3" t="n">
+        <v>0.553333333333333</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.466666666666667</v>
+      </c>
+      <c r="K3" t="n">
         <v>0.04</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.276666666666667</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.486666666666667</v>
+        <v>0.49</v>
       </c>
       <c r="M3" t="n">
-        <v>0.19</v>
+        <v>0.84</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0866666666666667</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.846666666666667</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.62</v>
+        <v>0.553333333333333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B4" t="n">
-        <v>0.926666666666667</v>
+        <v>0.993333333333333</v>
       </c>
       <c r="C4" t="n">
-        <v>0.706666666666667</v>
+        <v>0.743333333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>0.443333333333333</v>
+        <v>0.433333333333333</v>
       </c>
       <c r="E4" t="n">
-        <v>0.993333333333333</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>0.903333333333333</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.903333333333333</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.303333333333333</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.216666666666667</v>
+      </c>
+      <c r="L4" t="n">
         <v>0.0166666666666667</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.896666666666667</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="M4" t="n">
         <v>0.906666666666667</v>
       </c>
-      <c r="K4" t="n">
-        <v>0.263333333333333</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.03</v>
-      </c>
       <c r="N4" t="n">
-        <v>0.276666666666667</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.00333333333333333</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.923333333333333</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.01</v>
+        <v>0.00666666666666667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B5" t="n">
-        <v>0.483333333333333</v>
+        <v>0.47</v>
       </c>
       <c r="C5" t="n">
-        <v>0.936666666666667</v>
+        <v>0.95</v>
       </c>
       <c r="D5" t="n">
-        <v>0.403333333333333</v>
+        <v>0.386666666666667</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0933333333333333</v>
+        <v>0.0166666666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>0.123333333333333</v>
+        <v>0.883333333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>0.916666666666667</v>
+        <v>0.636666666666667</v>
       </c>
       <c r="H5" t="n">
-        <v>0.603333333333333</v>
+        <v>0.876666666666667</v>
       </c>
       <c r="I5" t="n">
-        <v>0.62</v>
+        <v>0.0533333333333333</v>
       </c>
       <c r="J5" t="n">
-        <v>0.903333333333333</v>
+        <v>0.00333333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00666666666666667</v>
+        <v>0.246666666666667</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.943333333333333</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00333333333333333</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.943333333333333</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.11</v>
+        <v>0.106666666666667</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B6" t="n">
-        <v>0.88</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>0.57</v>
+        <v>0.00333333333333333</v>
       </c>
       <c r="F6" t="n">
         <v>0.116666666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09</v>
+        <v>0.92</v>
       </c>
       <c r="H6" t="n">
-        <v>0.933333333333333</v>
+        <v>0.316666666666667</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>0.54</v>
       </c>
       <c r="J6" t="n">
-        <v>0.333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="K6" t="n">
+        <v>0.246666666666667</v>
+      </c>
+      <c r="L6" t="n">
         <v>0.55</v>
       </c>
-      <c r="L6" t="n">
-        <v>0.256666666666667</v>
-      </c>
       <c r="M6" t="n">
-        <v>0.0166666666666667</v>
+        <v>0.0766666666666667</v>
       </c>
       <c r="N6" t="n">
-        <v>0.303333333333333</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.566666666666667</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.0966666666666667</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.00333333333333333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="C7" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0766666666666667</v>
+        <v>0.0866666666666667</v>
       </c>
       <c r="E7" t="n">
-        <v>0.106666666666667</v>
+        <v>0.153333333333333</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0433333333333333</v>
+        <v>0.156666666666667</v>
       </c>
       <c r="G7" t="n">
-        <v>0.17</v>
+        <v>0.55</v>
       </c>
       <c r="H7" t="n">
-        <v>0.48</v>
+        <v>0.413333333333333</v>
       </c>
       <c r="I7" t="n">
-        <v>0.286666666666667</v>
+        <v>0.0466666666666667</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4</v>
+        <v>0.743333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04</v>
+        <v>0.793333333333333</v>
       </c>
       <c r="L7" t="n">
-        <v>0.71</v>
+        <v>0.56</v>
       </c>
       <c r="M7" t="n">
-        <v>0.613333333333333</v>
+        <v>0.853333333333333</v>
       </c>
       <c r="N7" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.813333333333333</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.0633333333333333</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="C8" t="n">
-        <v>0.926666666666667</v>
+        <v>0.936666666666667</v>
       </c>
       <c r="D8" t="n">
-        <v>0.396666666666667</v>
+        <v>0.423333333333333</v>
       </c>
       <c r="E8" t="n">
-        <v>0.463333333333333</v>
+        <v>0.00666666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05</v>
+        <v>0.39</v>
       </c>
       <c r="G8" t="n">
-        <v>0.373333333333333</v>
+        <v>0.103333333333333</v>
       </c>
       <c r="H8" t="n">
-        <v>0.116666666666667</v>
+        <v>0.36</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0866666666666667</v>
+        <v>0.196666666666667</v>
       </c>
       <c r="J8" t="n">
-        <v>0.356666666666667</v>
+        <v>0.64</v>
       </c>
       <c r="K8" t="n">
-        <v>0.15</v>
+        <v>0.103333333333333</v>
       </c>
       <c r="L8" t="n">
-        <v>0.576666666666667</v>
+        <v>0.393333333333333</v>
       </c>
       <c r="M8" t="n">
-        <v>0.16</v>
+        <v>0.836666666666667</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0933333333333333</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.413333333333333</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.883333333333333</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.393333333333333</v>
+        <v>0.363333333333333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0166666666666667</v>
+        <v>0.29</v>
       </c>
       <c r="C9" t="n">
-        <v>0.993333333333333</v>
+        <v>0.99</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>0.466666666666667</v>
       </c>
       <c r="E9" t="n">
-        <v>0.85</v>
+        <v>0.02</v>
       </c>
       <c r="F9" t="n">
-        <v>0.106666666666667</v>
+        <v>0.976666666666667</v>
       </c>
       <c r="G9" t="n">
-        <v>0.986666666666667</v>
+        <v>0.846666666666667</v>
       </c>
       <c r="H9" t="n">
-        <v>0.83</v>
+        <v>0.746666666666667</v>
       </c>
       <c r="I9" t="n">
-        <v>0.913333333333333</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="J9" t="n">
-        <v>0.77</v>
+        <v>0.0366666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01</v>
+        <v>0.286666666666667</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03</v>
+        <v>0.723333333333333</v>
       </c>
       <c r="M9" t="n">
-        <v>0.176666666666667</v>
+        <v>0.463333333333333</v>
       </c>
       <c r="N9" t="n">
-        <v>0.306666666666667</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.483333333333333</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.61</v>
+        <v>0.623333333333333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
-        <v>0.00666666666666667</v>
+        <v>0.00333333333333333</v>
       </c>
       <c r="C10" t="n">
-        <v>0.423333333333333</v>
+        <v>0.43</v>
       </c>
       <c r="D10" t="n">
-        <v>0.976666666666667</v>
+        <v>0.986666666666667</v>
       </c>
       <c r="E10" t="n">
-        <v>0.34</v>
+        <v>0.973333333333333</v>
       </c>
       <c r="F10" t="n">
-        <v>0.683333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="G10" t="n">
-        <v>0.763333333333333</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="H10" t="n">
-        <v>0.136666666666667</v>
+        <v>0.436666666666667</v>
       </c>
       <c r="I10" t="n">
-        <v>0.226666666666667</v>
+        <v>0.906666666666667</v>
       </c>
       <c r="J10" t="n">
-        <v>0.473333333333333</v>
+        <v>0.293333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>0.896666666666667</v>
+        <v>0.866666666666667</v>
       </c>
       <c r="L10" t="n">
-        <v>0.256666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="M10" t="n">
-        <v>0.97</v>
+        <v>0.353333333333333</v>
       </c>
       <c r="N10" t="n">
-        <v>0.876666666666667</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.56</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.306666666666667</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.72</v>
+        <v>0.696666666666667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
-        <v>0.673333333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="C11" t="n">
-        <v>0.156666666666667</v>
+        <v>0.143333333333333</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0266666666666667</v>
+        <v>0.0233333333333333</v>
       </c>
       <c r="E11" t="n">
-        <v>0.366666666666667</v>
+        <v>0.953333333333333</v>
       </c>
       <c r="F11" t="n">
-        <v>0.486666666666667</v>
+        <v>0.193333333333333</v>
       </c>
       <c r="G11" t="n">
-        <v>0.19</v>
+        <v>0.913333333333333</v>
       </c>
       <c r="H11" t="n">
-        <v>0.893333333333333</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="I11" t="n">
-        <v>0.59</v>
+        <v>0.586666666666667</v>
       </c>
       <c r="J11" t="n">
-        <v>0.146666666666667</v>
+        <v>0.186666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>0.553333333333333</v>
+        <v>0.09</v>
       </c>
       <c r="L11" t="n">
-        <v>0.196666666666667</v>
+        <v>0.52</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.513333333333333</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.683333333333333</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.84</v>
+        <v>0.816666666666667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B12" t="n">
-        <v>0.993333333333333</v>
+        <v>0.983333333333333</v>
       </c>
       <c r="C12" t="n">
         <v>0.976666666666667</v>
@@ -1061,732 +953,606 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.966666666666667</v>
+        <v>0.0366666666666667</v>
       </c>
       <c r="F12" t="n">
-        <v>0.37</v>
+        <v>0.57</v>
       </c>
       <c r="G12" t="n">
-        <v>0.57</v>
+        <v>0.21</v>
       </c>
       <c r="H12" t="n">
-        <v>0.193333333333333</v>
+        <v>0.336666666666667</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0233333333333333</v>
+        <v>0.0166666666666667</v>
       </c>
       <c r="J12" t="n">
-        <v>0.37</v>
+        <v>0.643333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>0.00666666666666667</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.64</v>
+        <v>0.976666666666667</v>
       </c>
       <c r="M12" t="n">
-        <v>0.00333333333333333</v>
+        <v>0.48</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.993333333333333</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.473333333333333</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.646666666666667</v>
+        <v>0.686666666666667</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0133333333333333</v>
+        <v>0.26</v>
       </c>
       <c r="C13" t="n">
-        <v>0.526666666666667</v>
+        <v>0.523333333333333</v>
       </c>
       <c r="D13" t="n">
-        <v>0.683333333333333</v>
+        <v>0.686666666666667</v>
       </c>
       <c r="E13" t="n">
-        <v>0.58</v>
+        <v>0.206666666666667</v>
       </c>
       <c r="F13" t="n">
-        <v>0.416666666666667</v>
+        <v>0.996666666666667</v>
       </c>
       <c r="G13" t="n">
-        <v>0.99</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.263333333333333</v>
       </c>
       <c r="I13" t="n">
-        <v>0.683333333333333</v>
+        <v>0.193333333333333</v>
       </c>
       <c r="J13" t="n">
-        <v>0.236666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="K13" t="n">
-        <v>0.22</v>
+        <v>0.973333333333333</v>
       </c>
       <c r="L13" t="n">
-        <v>0.116666666666667</v>
+        <v>0.436666666666667</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0366666666666667</v>
+        <v>0.51</v>
       </c>
       <c r="N13" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.456666666666667</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0266666666666667</v>
+        <v>0.0866666666666667</v>
       </c>
       <c r="C14" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="D14" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.95</v>
+        <v>0.983333333333333</v>
       </c>
       <c r="F14" t="n">
-        <v>0.926666666666667</v>
+        <v>0.996666666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0.81</v>
       </c>
       <c r="H14" t="n">
-        <v>0.813333333333333</v>
+        <v>0.306666666666667</v>
       </c>
       <c r="I14" t="n">
-        <v>0.186666666666667</v>
+        <v>0.786666666666667</v>
       </c>
       <c r="J14" t="n">
-        <v>0.293333333333333</v>
+        <v>0.51</v>
       </c>
       <c r="K14" t="n">
-        <v>0.813333333333333</v>
+        <v>0.02</v>
       </c>
       <c r="L14" t="n">
-        <v>0.486666666666667</v>
+        <v>0.523333333333333</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0.786666666666667</v>
       </c>
       <c r="N14" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.766666666666667</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.293333333333333</v>
+        <v>0.326666666666667</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B15" t="n">
-        <v>0.446666666666667</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.59</v>
+        <v>0.563333333333333</v>
       </c>
       <c r="D15" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="E15" t="n">
-        <v>0.936666666666667</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0333333333333333</v>
+        <v>0.866666666666667</v>
       </c>
       <c r="G15" t="n">
-        <v>0.856666666666667</v>
+        <v>0.22</v>
       </c>
       <c r="H15" t="n">
-        <v>0.246666666666667</v>
+        <v>0.953333333333333</v>
       </c>
       <c r="I15" t="n">
-        <v>0.69</v>
+        <v>0.143333333333333</v>
       </c>
       <c r="J15" t="n">
-        <v>0.95</v>
+        <v>0.94</v>
       </c>
       <c r="K15" t="n">
-        <v>0.163333333333333</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.936666666666667</v>
+        <v>0.316666666666667</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01</v>
+        <v>0.0133333333333333</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.246666666666667</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.0133333333333333</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.0366666666666667</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B16" t="n">
-        <v>0.966666666666667</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.89</v>
+        <v>0.903333333333333</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0933333333333333</v>
+        <v>0.08</v>
       </c>
       <c r="E16" t="n">
-        <v>0.976666666666667</v>
+        <v>0.103333333333333</v>
       </c>
       <c r="F16" t="n">
-        <v>0.706666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.106666666666667</v>
+        <v>0.353333333333333</v>
       </c>
       <c r="H16" t="n">
-        <v>0.37</v>
+        <v>0.633333333333333</v>
       </c>
       <c r="I16" t="n">
-        <v>0.786666666666667</v>
+        <v>0.476666666666667</v>
       </c>
       <c r="J16" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M16" t="n">
         <v>0.556666666666667</v>
       </c>
-      <c r="K16" t="n">
-        <v>0.476666666666667</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.816666666666667</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.01</v>
-      </c>
       <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.483333333333333</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.00666666666666667</v>
+        <v>0.0133333333333333</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B17" t="n">
-        <v>0.00333333333333333</v>
+        <v>0.363333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>0.21</v>
+        <v>0.193333333333333</v>
       </c>
       <c r="D17" t="n">
-        <v>0.876666666666667</v>
+        <v>0.863333333333333</v>
       </c>
       <c r="E17" t="n">
-        <v>0.996666666666667</v>
+        <v>0.69</v>
       </c>
       <c r="F17" t="n">
-        <v>0.893333333333333</v>
+        <v>0.92</v>
       </c>
       <c r="G17" t="n">
-        <v>0.916666666666667</v>
+        <v>0.0266666666666667</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0366666666666667</v>
+        <v>0.28</v>
       </c>
       <c r="I17" t="n">
-        <v>0.39</v>
+        <v>0.49</v>
       </c>
       <c r="J17" t="n">
-        <v>0.276666666666667</v>
+        <v>0.683333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>0.493333333333333</v>
+        <v>0.17</v>
       </c>
       <c r="L17" t="n">
-        <v>0.583333333333333</v>
+        <v>0.606666666666667</v>
       </c>
       <c r="M17" t="n">
-        <v>0.686666666666667</v>
+        <v>0.843333333333333</v>
       </c>
       <c r="N17" t="n">
-        <v>0.153333333333333</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.603333333333333</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.853333333333333</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.56</v>
+        <v>0.516666666666667</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B18" t="n">
-        <v>0.943333333333333</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.18</v>
+        <v>0.226666666666667</v>
       </c>
       <c r="D18" t="n">
-        <v>0.19</v>
+        <v>0.163333333333333</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.0133333333333333</v>
       </c>
       <c r="F18" t="n">
-        <v>0.126666666666667</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="G18" t="n">
-        <v>0.396666666666667</v>
+        <v>0.946666666666667</v>
       </c>
       <c r="H18" t="n">
-        <v>0.93</v>
+        <v>0.29</v>
       </c>
       <c r="I18" t="n">
-        <v>0.103333333333333</v>
+        <v>0.04</v>
       </c>
       <c r="J18" t="n">
-        <v>0.353333333333333</v>
+        <v>0.29</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0166666666666667</v>
+        <v>0.186666666666667</v>
       </c>
       <c r="L18" t="n">
-        <v>0.283333333333333</v>
+        <v>0.116666666666667</v>
       </c>
       <c r="M18" t="n">
-        <v>0.06</v>
+        <v>0.64</v>
       </c>
       <c r="N18" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.116666666666667</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.713333333333333</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.0466666666666667</v>
+        <v>0.0233333333333333</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B19" t="n">
-        <v>0.496666666666667</v>
+        <v>0.02</v>
       </c>
       <c r="C19" t="n">
-        <v>0.836666666666667</v>
+        <v>0.893333333333333</v>
       </c>
       <c r="D19" t="n">
-        <v>0.17</v>
+        <v>0.136666666666667</v>
       </c>
       <c r="E19" t="n">
-        <v>0.00333333333333333</v>
+        <v>0.57</v>
       </c>
       <c r="F19" t="n">
-        <v>0.556666666666667</v>
+        <v>0.116666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>0.176666666666667</v>
+        <v>0.79</v>
       </c>
       <c r="H19" t="n">
-        <v>0.81</v>
+        <v>0.313333333333333</v>
       </c>
       <c r="I19" t="n">
-        <v>0.156666666666667</v>
+        <v>0.433333333333333</v>
       </c>
       <c r="J19" t="n">
-        <v>0.246666666666667</v>
+        <v>0.276666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>0.43</v>
+        <v>0.366666666666667</v>
       </c>
       <c r="L19" t="n">
-        <v>0.286666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="M19" t="n">
-        <v>0.42</v>
+        <v>0.24</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.826666666666667</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.286666666666667</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.46</v>
+        <v>0.486666666666667</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B20" t="n">
-        <v>0.11</v>
+        <v>0.00333333333333333</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00666666666666667</v>
+        <v>0.0133333333333333</v>
       </c>
       <c r="D20" t="n">
-        <v>0.98</v>
+        <v>0.966666666666667</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.976666666666667</v>
       </c>
       <c r="F20" t="n">
-        <v>0.936666666666667</v>
+        <v>0.276666666666667</v>
       </c>
       <c r="G20" t="n">
-        <v>0.32</v>
+        <v>0.0466666666666667</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0466666666666667</v>
+        <v>0.776666666666667</v>
       </c>
       <c r="I20" t="n">
+        <v>0.456666666666667</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.846666666666667</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.706666666666667</v>
+      </c>
+      <c r="L20" t="n">
         <v>0.623333333333333</v>
       </c>
-      <c r="J20" t="n">
-        <v>0.733333333333333</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.816666666666667</v>
-      </c>
       <c r="M20" t="n">
-        <v>0.743333333333333</v>
+        <v>0.0766666666666667</v>
       </c>
       <c r="N20" t="n">
-        <v>0.736666666666667</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.533333333333333</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="D21" t="n">
-        <v>0.853333333333333</v>
+        <v>0.863333333333333</v>
       </c>
       <c r="E21" t="n">
-        <v>0.373333333333333</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0.983333333333333</v>
+        <v>0.47</v>
       </c>
       <c r="G21" t="n">
-        <v>0.466666666666667</v>
+        <v>0.13</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0933333333333333</v>
+        <v>0.413333333333333</v>
       </c>
       <c r="I21" t="n">
-        <v>0.713333333333333</v>
+        <v>0.78</v>
       </c>
       <c r="J21" t="n">
-        <v>0.41</v>
+        <v>0.126666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>0.75</v>
+        <v>0.02</v>
       </c>
       <c r="L21" t="n">
-        <v>0.12</v>
+        <v>0.266666666666667</v>
       </c>
       <c r="M21" t="n">
-        <v>0.993333333333333</v>
+        <v>0.16</v>
       </c>
       <c r="N21" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.313333333333333</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.216666666666667</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.163333333333333</v>
+        <v>0.153333333333333</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B22" t="n">
-        <v>0.97</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="C22" t="n">
-        <v>0.42</v>
+        <v>0.373333333333333</v>
       </c>
       <c r="D22" t="n">
-        <v>0.826666666666667</v>
+        <v>0.79</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0733333333333333</v>
+        <v>0.976666666666667</v>
       </c>
       <c r="F22" t="n">
-        <v>0.236666666666667</v>
+        <v>0.07</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0466666666666667</v>
+        <v>0.69</v>
       </c>
       <c r="H22" t="n">
-        <v>0.65</v>
+        <v>0.626666666666667</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0533333333333333</v>
+        <v>0.92</v>
       </c>
       <c r="J22" t="n">
-        <v>0.64</v>
+        <v>0.233333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>0.92</v>
+        <v>0.68</v>
       </c>
       <c r="L22" t="n">
-        <v>0.173333333333333</v>
+        <v>0.553333333333333</v>
       </c>
       <c r="M22" t="n">
-        <v>0.763333333333333</v>
+        <v>0.606666666666667</v>
       </c>
       <c r="N22" t="n">
-        <v>0.653333333333333</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.576666666666667</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0.696666666666667</v>
-      </c>
-      <c r="Q22" t="n">
         <v>0.903333333333333</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B23" t="n">
-        <v>0.786666666666667</v>
+        <v>0.986666666666667</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04</v>
+        <v>0.0566666666666667</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.99</v>
+        <v>0.94</v>
       </c>
       <c r="F23" t="n">
-        <v>0.956666666666667</v>
+        <v>0.05</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0533333333333333</v>
+        <v>0.08</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0733333333333333</v>
+        <v>0.946666666666667</v>
       </c>
       <c r="I23" t="n">
-        <v>0.67</v>
+        <v>0.246666666666667</v>
       </c>
       <c r="J23" t="n">
-        <v>0.95</v>
+        <v>0.423333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>0.276666666666667</v>
+        <v>0.00333333333333333</v>
       </c>
       <c r="L23" t="n">
-        <v>0.49</v>
+        <v>0.926666666666667</v>
       </c>
       <c r="M23" t="n">
-        <v>0.513333333333333</v>
+        <v>0.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0.00666666666666667</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.94</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.903333333333333</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.686666666666667</v>
+        <v>0.746666666666667</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B24" t="n">
-        <v>0.156666666666667</v>
+        <v>0.14</v>
       </c>
       <c r="C24" t="n">
-        <v>0.746666666666667</v>
+        <v>0.71</v>
       </c>
       <c r="D24" t="n">
-        <v>0.403333333333333</v>
+        <v>0.373333333333333</v>
       </c>
       <c r="E24" t="n">
-        <v>0.27</v>
+        <v>0.97</v>
       </c>
       <c r="F24" t="n">
-        <v>0.993333333333333</v>
+        <v>0.106666666666667</v>
       </c>
       <c r="G24" t="n">
-        <v>0.116666666666667</v>
+        <v>0.00333333333333333</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.0433333333333333</v>
       </c>
       <c r="I24" t="n">
-        <v>0.123333333333333</v>
+        <v>0.813333333333333</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0233333333333333</v>
+        <v>0.223333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>0.826666666666667</v>
+        <v>0.05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.18</v>
+        <v>0.7</v>
       </c>
       <c r="M24" t="n">
-        <v>0.453333333333333</v>
+        <v>0.0933333333333333</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.703333333333333</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0.0966666666666667</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0.236666666666667</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="C25" t="n">
-        <v>0.956666666666667</v>
+        <v>0.943333333333333</v>
       </c>
       <c r="D25" t="n">
-        <v>0.956666666666667</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0.983333333333333</v>
       </c>
       <c r="F25" t="n">
-        <v>0.826666666666667</v>
+        <v>0.08</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0633333333333333</v>
+        <v>0.21</v>
       </c>
       <c r="H25" t="n">
-        <v>0.223333333333333</v>
+        <v>0.316666666666667</v>
       </c>
       <c r="I25" t="n">
-        <v>0.45</v>
+        <v>0.676666666666667</v>
       </c>
       <c r="J25" t="n">
-        <v>0.35</v>
+        <v>0.376666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>0.72</v>
+        <v>0.113333333333333</v>
       </c>
       <c r="L25" t="n">
-        <v>0.386666666666667</v>
+        <v>0.586666666666667</v>
       </c>
       <c r="M25" t="n">
-        <v>0.783333333333333</v>
+        <v>0.95</v>
       </c>
       <c r="N25" t="n">
-        <v>0.146666666666667</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.556666666666667</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0.936666666666667</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
     </row>
   </sheetData>
@@ -1843,1286 +1609,1061 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.296666666666667</v>
+        <v>0.286666666666667</v>
       </c>
       <c r="D2" t="n">
-        <v>0.793333333333333</v>
+        <v>0.766666666666667</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.973333333333333</v>
       </c>
       <c r="F2" t="n">
-        <v>0.993333333333333</v>
+        <v>0.19</v>
       </c>
       <c r="G2" t="n">
-        <v>0.183333333333333</v>
+        <v>0.64</v>
       </c>
       <c r="H2" t="n">
-        <v>0.626666666666667</v>
+        <v>0.116666666666667</v>
       </c>
       <c r="I2" t="n">
-        <v>0.56</v>
+        <v>0.886666666666667</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06</v>
+        <v>0.683333333333333</v>
       </c>
       <c r="K2" t="n">
-        <v>0.883333333333333</v>
+        <v>0.996666666666667</v>
       </c>
       <c r="L2" t="n">
-        <v>0.693333333333333</v>
+        <v>0.466666666666667</v>
       </c>
       <c r="M2" t="n">
-        <v>0.666666666666667</v>
+        <v>0.393333333333333</v>
       </c>
       <c r="N2" t="n">
-        <v>0.996666666666667</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.443333333333333</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.293333333333333</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.83</v>
+        <v>0.856666666666667</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B3" t="n">
-        <v>0.856666666666667</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.676666666666667</v>
+        <v>0.69</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0166666666666667</v>
+        <v>0.92</v>
       </c>
       <c r="F3" t="n">
-        <v>0.846666666666667</v>
+        <v>0.733333333333333</v>
       </c>
       <c r="G3" t="n">
-        <v>0.61</v>
+        <v>0.643333333333333</v>
       </c>
       <c r="H3" t="n">
-        <v>0.626666666666667</v>
+        <v>0.763333333333333</v>
       </c>
       <c r="I3" t="n">
-        <v>0.156666666666667</v>
+        <v>0.98</v>
       </c>
       <c r="J3" t="n">
-        <v>0.756666666666667</v>
+        <v>0.736666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>0.986666666666667</v>
+        <v>0.396666666666667</v>
       </c>
       <c r="L3" t="n">
-        <v>0.77</v>
+        <v>0.63</v>
       </c>
       <c r="M3" t="n">
-        <v>0.85</v>
+        <v>0.0266666666666667</v>
       </c>
       <c r="N3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.593333333333333</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.0366666666666667</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.803333333333333</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0266666666666667</v>
+        <v>0.00333333333333333</v>
       </c>
       <c r="C4" t="n">
+        <v>0.593333333333333</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.653333333333333</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.943333333333333</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J4" t="n">
         <v>0.646666666666667</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.643333333333333</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.0366666666666667</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.493333333333333</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.773333333333333</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.286666666666667</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.09</v>
-      </c>
       <c r="K4" t="n">
-        <v>0.956666666666667</v>
+        <v>0.503333333333333</v>
       </c>
       <c r="L4" t="n">
-        <v>0.63</v>
+        <v>0.943333333333333</v>
       </c>
       <c r="M4" t="n">
-        <v>0.97</v>
+        <v>0.23</v>
       </c>
       <c r="N4" t="n">
-        <v>0.463333333333333</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.923333333333333</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.183333333333333</v>
-      </c>
-      <c r="Q4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1</v>
+        <v>0.42</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.673333333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="E5" t="n">
-        <v>0.853333333333333</v>
+        <v>0.866666666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>0.756666666666667</v>
+        <v>0.00333333333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.403333333333333</v>
       </c>
       <c r="H5" t="n">
-        <v>0.373333333333333</v>
+        <v>0.08</v>
       </c>
       <c r="I5" t="n">
-        <v>0.113333333333333</v>
+        <v>0.83</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0366666666666667</v>
+        <v>0.956666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>0.72</v>
+        <v>0.953333333333333</v>
       </c>
       <c r="L5" t="n">
-        <v>0.98</v>
+        <v>0.596666666666667</v>
       </c>
       <c r="M5" t="n">
-        <v>0.96</v>
+        <v>0.146666666666667</v>
       </c>
       <c r="N5" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.553333333333333</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.97</v>
+        <v>0.956666666666667</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B6" t="n">
-        <v>0.156666666666667</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00333333333333333</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="E6" t="n">
-        <v>0.59</v>
+        <v>0.79</v>
       </c>
       <c r="F6" t="n">
-        <v>0.946666666666667</v>
+        <v>0.38</v>
       </c>
       <c r="G6" t="n">
-        <v>0.33</v>
+        <v>0.05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04</v>
+        <v>0.433333333333333</v>
       </c>
       <c r="I6" t="n">
-        <v>0.126666666666667</v>
+        <v>0.856666666666667</v>
       </c>
       <c r="J6" t="n">
-        <v>0.413333333333333</v>
+        <v>0.836666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>0.846666666666667</v>
+        <v>0.77</v>
       </c>
       <c r="L6" t="n">
-        <v>0.823333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0.64</v>
+        <v>0.993333333333333</v>
       </c>
       <c r="N6" t="n">
-        <v>0.776666666666667</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.253333333333333</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.996666666666667</v>
-      </c>
-      <c r="Q6" t="n">
         <v>0.966666666666667</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0266666666666667</v>
+        <v>0.293333333333333</v>
       </c>
       <c r="C7" t="n">
-        <v>0.733333333333333</v>
+        <v>0.763333333333333</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.873333333333333</v>
+        <v>0.143333333333333</v>
       </c>
       <c r="F7" t="n">
-        <v>0.513333333333333</v>
+        <v>0.603333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>0.603333333333333</v>
+        <v>0.0866666666666667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0966666666666667</v>
+        <v>0.206666666666667</v>
       </c>
       <c r="I7" t="n">
-        <v>0.603333333333333</v>
+        <v>0.783333333333333</v>
       </c>
       <c r="J7" t="n">
-        <v>0.236666666666667</v>
+        <v>0.03</v>
       </c>
       <c r="K7" t="n">
-        <v>0.763333333333333</v>
+        <v>0.193333333333333</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0133333333333333</v>
+        <v>0.686666666666667</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0466666666666667</v>
+        <v>0.256666666666667</v>
       </c>
       <c r="N7" t="n">
-        <v>0.216666666666667</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.733333333333333</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.266666666666667</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.796666666666667</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0166666666666667</v>
+        <v>0.0433333333333333</v>
       </c>
       <c r="C8" t="n">
-        <v>0.186666666666667</v>
+        <v>0.21</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7</v>
+        <v>0.676666666666667</v>
       </c>
       <c r="E8" t="n">
-        <v>0.303333333333333</v>
+        <v>0.973333333333333</v>
       </c>
       <c r="F8" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="K8" t="n">
         <v>0.986666666666667</v>
       </c>
-      <c r="G8" t="n">
-        <v>0.623333333333333</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.966666666666667</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.313333333333333</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.81</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.22</v>
+        <v>0.796666666666667</v>
       </c>
       <c r="M8" t="n">
-        <v>0.896666666666667</v>
+        <v>0.193333333333333</v>
       </c>
       <c r="N8" t="n">
-        <v>0.993333333333333</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.846666666666667</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.223333333333333</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.673333333333333</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0.636666666666667</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0233333333333333</v>
+        <v>0.0166666666666667</v>
       </c>
       <c r="D9" t="n">
-        <v>0.71</v>
+        <v>0.703333333333333</v>
       </c>
       <c r="E9" t="n">
+        <v>0.936666666666667</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.363333333333333</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.263333333333333</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.446666666666667</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.743333333333333</v>
+      </c>
+      <c r="K9" t="n">
         <v>0.0566666666666667</v>
       </c>
-      <c r="F9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="L9" t="n">
+        <v>0.243333333333333</v>
+      </c>
+      <c r="M9" t="n">
         <v>0.373333333333333</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0366666666666667</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.403333333333333</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.946666666666667</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.683333333333333</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.92</v>
-      </c>
       <c r="N9" t="n">
-        <v>0.0533333333333333</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.286666666666667</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.416666666666667</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.156666666666667</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
-        <v>0.99</v>
+        <v>0.986666666666667</v>
       </c>
       <c r="C10" t="n">
-        <v>0.663333333333333</v>
+        <v>0.72</v>
       </c>
       <c r="D10" t="n">
         <v>0.0466666666666667</v>
       </c>
       <c r="E10" t="n">
-        <v>0.32</v>
+        <v>0.0433333333333333</v>
       </c>
       <c r="F10" t="n">
-        <v>0.39</v>
+        <v>0.123333333333333</v>
       </c>
       <c r="G10" t="n">
-        <v>0.156666666666667</v>
+        <v>0.76</v>
       </c>
       <c r="H10" t="n">
-        <v>0.823333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>0.96</v>
+        <v>0.2</v>
       </c>
       <c r="J10" t="n">
-        <v>0.726666666666667</v>
+        <v>0.82</v>
       </c>
       <c r="K10" t="n">
-        <v>0.196666666666667</v>
+        <v>0.19</v>
       </c>
       <c r="L10" t="n">
-        <v>0.853333333333333</v>
+        <v>0.47</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0366666666666667</v>
+        <v>0.403333333333333</v>
       </c>
       <c r="N10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.483333333333333</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.373333333333333</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.07</v>
+        <v>0.0633333333333333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0466666666666667</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="C11" t="n">
-        <v>0.583333333333333</v>
+        <v>0.563333333333333</v>
       </c>
       <c r="D11" t="n">
-        <v>0.993333333333333</v>
+        <v>0.983333333333333</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0866666666666667</v>
+        <v>0.0233333333333333</v>
       </c>
       <c r="F11" t="n">
-        <v>0.78</v>
+        <v>0.653333333333333</v>
       </c>
       <c r="G11" t="n">
-        <v>0.61</v>
+        <v>0.126666666666667</v>
       </c>
       <c r="H11" t="n">
-        <v>0.146666666666667</v>
+        <v>0.326666666666667</v>
       </c>
       <c r="I11" t="n">
-        <v>0.706666666666667</v>
+        <v>0.743333333333333</v>
       </c>
       <c r="J11" t="n">
-        <v>0.356666666666667</v>
+        <v>0.373333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>0.716666666666667</v>
+        <v>0.55</v>
       </c>
       <c r="L11" t="n">
-        <v>0.32</v>
+        <v>0.373333333333333</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>0.686666666666667</v>
       </c>
       <c r="N11" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.296666666666667</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.273333333333333</v>
+        <v>0.223333333333333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B12" t="n">
-        <v>0.00333333333333333</v>
+        <v>0.01</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0166666666666667</v>
+        <v>0.03</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0966666666666667</v>
+        <v>0.97</v>
       </c>
       <c r="F12" t="n">
-        <v>0.103333333333333</v>
+        <v>0.383333333333333</v>
       </c>
       <c r="G12" t="n">
-        <v>0.396666666666667</v>
+        <v>0.68</v>
       </c>
       <c r="H12" t="n">
-        <v>0.776666666666667</v>
+        <v>0.696666666666667</v>
       </c>
       <c r="I12" t="n">
-        <v>0.54</v>
+        <v>0.853333333333333</v>
       </c>
       <c r="J12" t="n">
-        <v>0.693333333333333</v>
+        <v>0.43</v>
       </c>
       <c r="K12" t="n">
-        <v>0.853333333333333</v>
+        <v>0.976666666666667</v>
       </c>
       <c r="L12" t="n">
-        <v>0.536666666666667</v>
+        <v>0.126666666666667</v>
       </c>
       <c r="M12" t="n">
-        <v>0.98</v>
+        <v>0.233333333333333</v>
       </c>
       <c r="N12" t="n">
-        <v>0.993333333333333</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.156666666666667</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.56</v>
+        <v>0.503333333333333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B13" t="n">
-        <v>0.966666666666667</v>
+        <v>0.79</v>
       </c>
       <c r="C13" t="n">
-        <v>0.23</v>
+        <v>0.236666666666667</v>
       </c>
       <c r="D13" t="n">
-        <v>0.393333333333333</v>
+        <v>0.486666666666667</v>
       </c>
       <c r="E13" t="n">
-        <v>0.243333333333333</v>
+        <v>0.55</v>
       </c>
       <c r="F13" t="n">
-        <v>0.37</v>
+        <v>0.00333333333333333</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00333333333333333</v>
+        <v>0.713333333333333</v>
       </c>
       <c r="H13" t="n">
-        <v>0.713333333333333</v>
+        <v>0.19</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0533333333333333</v>
+        <v>0.993333333333333</v>
       </c>
       <c r="J13" t="n">
-        <v>0.18</v>
+        <v>0.633333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>0.976666666666667</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.71</v>
+        <v>0.516666666666667</v>
       </c>
       <c r="M13" t="n">
-        <v>0.833333333333333</v>
+        <v>0.696666666666667</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.516666666666667</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.656666666666667</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.92</v>
+        <v>0.926666666666667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B14" t="n">
-        <v>0.97</v>
+        <v>0.9</v>
       </c>
       <c r="C14" t="n">
         <v>0.81</v>
       </c>
       <c r="D14" t="n">
-        <v>0.926666666666667</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0633333333333333</v>
+        <v>0.03</v>
       </c>
       <c r="F14" t="n">
-        <v>0.223333333333333</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.506666666666667</v>
       </c>
       <c r="H14" t="n">
-        <v>0.49</v>
+        <v>0.153333333333333</v>
       </c>
       <c r="I14" t="n">
-        <v>0.976666666666667</v>
+        <v>0.0266666666666667</v>
       </c>
       <c r="J14" t="n">
-        <v>0.103333333333333</v>
+        <v>0.336666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0133333333333333</v>
+        <v>0.756666666666667</v>
       </c>
       <c r="L14" t="n">
-        <v>0.29</v>
+        <v>0.656666666666667</v>
       </c>
       <c r="M14" t="n">
-        <v>0.04</v>
+        <v>0.433333333333333</v>
       </c>
       <c r="N14" t="n">
-        <v>0.783333333333333</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.576666666666667</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.793333333333333</v>
+        <v>0.803333333333333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0466666666666667</v>
+        <v>0.0433333333333333</v>
       </c>
       <c r="D15" t="n">
-        <v>0.846666666666667</v>
+        <v>0.813333333333333</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0766666666666667</v>
+        <v>0.943333333333333</v>
       </c>
       <c r="F15" t="n">
-        <v>0.856666666666667</v>
+        <v>0.313333333333333</v>
       </c>
       <c r="G15" t="n">
-        <v>0.353333333333333</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0.19</v>
       </c>
       <c r="I15" t="n">
-        <v>0.513333333333333</v>
+        <v>0.81</v>
       </c>
       <c r="J15" t="n">
-        <v>0.166666666666667</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>0.793333333333333</v>
+        <v>0.983333333333333</v>
       </c>
       <c r="L15" t="n">
-        <v>0.156666666666667</v>
+        <v>0.82</v>
       </c>
       <c r="M15" t="n">
-        <v>0.966666666666667</v>
+        <v>0.82</v>
       </c>
       <c r="N15" t="n">
-        <v>0.983333333333333</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.8</v>
+        <v>0.766666666666667</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B16" t="n">
-        <v>0.206666666666667</v>
+        <v>0.01</v>
       </c>
       <c r="C16" t="n">
-        <v>0.113333333333333</v>
+        <v>0.15</v>
       </c>
       <c r="D16" t="n">
-        <v>0.99</v>
+        <v>0.986666666666667</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0166666666666667</v>
+        <v>0.976666666666667</v>
       </c>
       <c r="F16" t="n">
-        <v>0.713333333333333</v>
+        <v>0.64</v>
       </c>
       <c r="G16" t="n">
-        <v>0.673333333333333</v>
+        <v>0.753333333333333</v>
       </c>
       <c r="H16" t="n">
-        <v>0.733333333333333</v>
+        <v>0.396666666666667</v>
       </c>
       <c r="I16" t="n">
-        <v>0.323333333333333</v>
+        <v>0.616666666666667</v>
       </c>
       <c r="J16" t="n">
-        <v>0.343333333333333</v>
+        <v>0.176666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>0.583333333333333</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0.233333333333333</v>
+        <v>0.126666666666667</v>
       </c>
       <c r="M16" t="n">
-        <v>0.983333333333333</v>
+        <v>0.24</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.266666666666667</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.986666666666667</v>
+        <v>0.973333333333333</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C17" t="n">
-        <v>0.553333333333333</v>
+        <v>0.59</v>
       </c>
       <c r="D17" t="n">
-        <v>0.28</v>
+        <v>0.253333333333333</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03</v>
+        <v>0.0466666666666667</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.0766666666666667</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0966666666666667</v>
+        <v>0.79</v>
       </c>
       <c r="H17" t="n">
-        <v>0.813333333333333</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="I17" t="n">
-        <v>0.623333333333333</v>
+        <v>0.72</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9</v>
+        <v>0.636666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>0.78</v>
+        <v>0.756666666666667</v>
       </c>
       <c r="L17" t="n">
-        <v>0.613333333333333</v>
+        <v>0.213333333333333</v>
       </c>
       <c r="M17" t="n">
-        <v>0.306666666666667</v>
+        <v>0.07</v>
       </c>
       <c r="N17" t="n">
-        <v>0.803333333333333</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.246666666666667</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.0733333333333333</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.483333333333333</v>
+        <v>0.516666666666667</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.876666666666667</v>
+        <v>0.886666666666667</v>
       </c>
       <c r="D18" t="n">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.86</v>
       </c>
       <c r="F18" t="n">
-        <v>0.396666666666667</v>
+        <v>0.796666666666667</v>
       </c>
       <c r="G18" t="n">
-        <v>0.773333333333333</v>
+        <v>0.26</v>
       </c>
       <c r="H18" t="n">
-        <v>0.23</v>
+        <v>0.136666666666667</v>
       </c>
       <c r="I18" t="n">
-        <v>0.796666666666667</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.153333333333333</v>
+        <v>0.756666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="L18" t="n">
-        <v>0.78</v>
+        <v>0.94</v>
       </c>
       <c r="M18" t="n">
-        <v>0.68</v>
+        <v>0.0633333333333333</v>
       </c>
       <c r="N18" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.946666666666667</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.98</v>
+        <v>0.976666666666667</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B19" t="n">
-        <v>0.423333333333333</v>
+        <v>0.95</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01</v>
+        <v>0.0166666666666667</v>
       </c>
       <c r="D19" t="n">
-        <v>0.89</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="E19" t="n">
-        <v>0.97</v>
+        <v>0.343333333333333</v>
       </c>
       <c r="F19" t="n">
-        <v>0.573333333333333</v>
+        <v>0.66</v>
       </c>
       <c r="G19" t="n">
-        <v>0.643333333333333</v>
+        <v>0.03</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0233333333333333</v>
+        <v>0.81</v>
       </c>
       <c r="I19" t="n">
-        <v>0.74</v>
+        <v>0.36</v>
       </c>
       <c r="J19" t="n">
-        <v>0.823333333333333</v>
+        <v>0.926666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>0.386666666666667</v>
+        <v>0.193333333333333</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9</v>
+        <v>0.113333333333333</v>
       </c>
       <c r="M19" t="n">
-        <v>0.51</v>
+        <v>0.443333333333333</v>
       </c>
       <c r="N19" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.106666666666667</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.396666666666667</v>
+        <v>0.346666666666667</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B20" t="n">
-        <v>0.496666666666667</v>
+        <v>0.776666666666667</v>
       </c>
       <c r="C20" t="n">
-        <v>0.803333333333333</v>
+        <v>0.826666666666667</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0433333333333333</v>
+        <v>0.04</v>
       </c>
       <c r="E20" t="n">
-        <v>0.98</v>
+        <v>0.02</v>
       </c>
       <c r="F20" t="n">
-        <v>0.00333333333333333</v>
+        <v>0.37</v>
       </c>
       <c r="G20" t="n">
-        <v>0.373333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="H20" t="n">
-        <v>0.73</v>
+        <v>0.393333333333333</v>
       </c>
       <c r="I20" t="n">
-        <v>0.236666666666667</v>
+        <v>0.36</v>
       </c>
       <c r="J20" t="n">
-        <v>0.353333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>0.256666666666667</v>
+        <v>0.306666666666667</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0633333333333333</v>
+        <v>0.56</v>
       </c>
       <c r="M20" t="n">
-        <v>0.18</v>
+        <v>0.97</v>
       </c>
       <c r="N20" t="n">
-        <v>0.296666666666667</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.553333333333333</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.946666666666667</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.16</v>
+        <v>0.143333333333333</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B21" t="n">
-        <v>0.99</v>
+        <v>0.906666666666667</v>
       </c>
       <c r="C21" t="n">
-        <v>0.736666666666667</v>
+        <v>0.77</v>
       </c>
       <c r="D21" t="n">
         <v>0.00333333333333333</v>
       </c>
       <c r="E21" t="n">
-        <v>0.556666666666667</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0166666666666667</v>
+        <v>0.573333333333333</v>
       </c>
       <c r="G21" t="n">
-        <v>0.59</v>
+        <v>0.493333333333333</v>
       </c>
       <c r="H21" t="n">
-        <v>0.436666666666667</v>
+        <v>0.48</v>
       </c>
       <c r="I21" t="n">
-        <v>0.64</v>
+        <v>0.01</v>
       </c>
       <c r="J21" t="n">
-        <v>0.446666666666667</v>
+        <v>0.12</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00666666666666667</v>
+        <v>0.873333333333333</v>
       </c>
       <c r="L21" t="n">
-        <v>0.146666666666667</v>
+        <v>0.893333333333333</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>0.926666666666667</v>
       </c>
       <c r="N21" t="n">
-        <v>0.886666666666667</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.896666666666667</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.923333333333333</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.836666666666667</v>
+        <v>0.776666666666667</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B22" t="n">
-        <v>0.13</v>
+        <v>0.83</v>
       </c>
       <c r="C22" t="n">
-        <v>0.85</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="D22" t="n">
-        <v>0.536666666666667</v>
+        <v>0.456666666666667</v>
       </c>
       <c r="E22" t="n">
-        <v>0.886666666666667</v>
+        <v>0.08</v>
       </c>
       <c r="F22" t="n">
-        <v>0.746666666666667</v>
+        <v>0.893333333333333</v>
       </c>
       <c r="G22" t="n">
-        <v>0.836666666666667</v>
+        <v>0.81</v>
       </c>
       <c r="H22" t="n">
-        <v>0.843333333333333</v>
+        <v>0.436666666666667</v>
       </c>
       <c r="I22" t="n">
-        <v>0.923333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
-        <v>0.506666666666667</v>
+        <v>0.933333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>0.21</v>
+        <v>0.253333333333333</v>
       </c>
       <c r="L22" t="n">
-        <v>0.916666666666667</v>
+        <v>0.67</v>
       </c>
       <c r="M22" t="n">
-        <v>0.00333333333333333</v>
+        <v>0.0366666666666667</v>
       </c>
       <c r="N22" t="n">
-        <v>0.226666666666667</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.706666666666667</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0.0133333333333333</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.136666666666667</v>
+        <v>0.143333333333333</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B23" t="n">
-        <v>0.6</v>
+        <v>0.0266666666666667</v>
       </c>
       <c r="C23" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0166666666666667</v>
+        <v>0.963333333333333</v>
       </c>
       <c r="G23" t="n">
-        <v>0.976666666666667</v>
+        <v>0.766666666666667</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8</v>
+        <v>0.00333333333333333</v>
       </c>
       <c r="I23" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.396666666666667</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.983333333333333</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.113333333333333</v>
+      </c>
+      <c r="M23" t="n">
         <v>0.463333333333333</v>
       </c>
-      <c r="J23" t="n">
-        <v>0.00666666666666667</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.496666666666667</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.446666666666667</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.46</v>
-      </c>
       <c r="N23" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.0933333333333333</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.21</v>
+        <v>0.183333333333333</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.196666666666667</v>
+        <v>0.17</v>
       </c>
       <c r="D24" t="n">
-        <v>0.17</v>
+        <v>0.173333333333333</v>
       </c>
       <c r="E24" t="n">
-        <v>0.216666666666667</v>
+        <v>0.06</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0766666666666667</v>
+        <v>0.753333333333333</v>
       </c>
       <c r="G24" t="n">
-        <v>0.696666666666667</v>
+        <v>0.66</v>
       </c>
       <c r="H24" t="n">
-        <v>0.643333333333333</v>
+        <v>0.936666666666667</v>
       </c>
       <c r="I24" t="n">
-        <v>0.883333333333333</v>
+        <v>0.203333333333333</v>
       </c>
       <c r="J24" t="n">
-        <v>0.956666666666667</v>
+        <v>0.173333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>0.223333333333333</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="L24" t="n">
-        <v>0.233333333333333</v>
+        <v>0.413333333333333</v>
       </c>
       <c r="M24" t="n">
-        <v>0.393333333333333</v>
+        <v>0.846666666666667</v>
       </c>
       <c r="N24" t="n">
-        <v>0.856666666666667</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0.796666666666667</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0.923333333333333</v>
+        <v>0.886666666666667</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B25" t="n">
-        <v>0.98</v>
+        <v>0.963333333333333</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.0933333333333333</v>
       </c>
       <c r="D25" t="n">
-        <v>0.146666666666667</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="E25" t="n">
-        <v>0.173333333333333</v>
+        <v>0.01</v>
       </c>
       <c r="F25" t="n">
-        <v>0.196666666666667</v>
+        <v>0.886666666666667</v>
       </c>
       <c r="G25" t="n">
-        <v>0.85</v>
+        <v>0.546666666666667</v>
       </c>
       <c r="H25" t="n">
-        <v>0.543333333333333</v>
+        <v>0.483333333333333</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>0.446666666666667</v>
       </c>
       <c r="J25" t="n">
-        <v>0.453333333333333</v>
+        <v>0.646666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>0.436666666666667</v>
+        <v>0.856666666666667</v>
       </c>
       <c r="L25" t="n">
-        <v>0.673333333333333</v>
+        <v>0.53</v>
       </c>
       <c r="M25" t="n">
-        <v>0.00333333333333333</v>
+        <v>0.106666666666667</v>
       </c>
       <c r="N25" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.496666666666667</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0.113333333333333</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.48</v>
+        <v>0.486666666666667</v>
       </c>
     </row>
   </sheetData>
